--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121355675</v>
       </c>
       <c r="B2" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355740</v>
+        <v>121355446</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571385</v>
+        <v>571453</v>
       </c>
       <c r="R3" t="n">
-        <v>6450505</v>
+        <v>6450543</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,17 +863,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355446</v>
+        <v>121355471</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +900,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571453</v>
+        <v>571429</v>
       </c>
       <c r="R4" t="n">
-        <v>6450543</v>
+        <v>6450550</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355471</v>
+        <v>121355740</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>56563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,42 +1012,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571429</v>
+        <v>571385</v>
       </c>
       <c r="R5" t="n">
-        <v>6450550</v>
+        <v>6450505</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>En tjäderhona med fyra kycklingar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355471</v>
+        <v>121355740</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +900,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571429</v>
+        <v>571385</v>
       </c>
       <c r="R4" t="n">
-        <v>6450550</v>
+        <v>6450505</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>En tjäderhona med fyra kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355740</v>
+        <v>121355471</v>
       </c>
       <c r="B5" t="n">
-        <v>56563</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,46 +1015,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571385</v>
+        <v>571429</v>
       </c>
       <c r="R5" t="n">
-        <v>6450505</v>
+        <v>6450550</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En tjäderhona med fyra kycklingar</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355740</v>
+        <v>121355471</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,46 +900,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571385</v>
+        <v>571429</v>
       </c>
       <c r="R4" t="n">
-        <v>6450505</v>
+        <v>6450550</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En tjäderhona med fyra kycklingar</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355471</v>
+        <v>121355740</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>56563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,42 +1012,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571429</v>
+        <v>571385</v>
       </c>
       <c r="R5" t="n">
-        <v>6450550</v>
+        <v>6450505</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>En tjäderhona med fyra kycklingar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355446</v>
+        <v>121355471</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571453</v>
+        <v>571429</v>
       </c>
       <c r="R3" t="n">
-        <v>6450543</v>
+        <v>6450550</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355471</v>
+        <v>121355446</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +906,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571429</v>
+        <v>571453</v>
       </c>
       <c r="R4" t="n">
-        <v>6450550</v>
+        <v>6450543</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355675</v>
+        <v>121355446</v>
       </c>
       <c r="B2" t="n">
-        <v>94700</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571398</v>
+        <v>571453</v>
       </c>
       <c r="R2" t="n">
-        <v>6450585</v>
+        <v>6450543</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,7 +784,7 @@
         <v>121355471</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355446</v>
+        <v>121355740</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,41 +905,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571453</v>
+        <v>571385</v>
       </c>
       <c r="R4" t="n">
-        <v>6450543</v>
+        <v>6450505</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,13 +979,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B5" t="n">
-        <v>56563</v>
+        <v>94712</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,42 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R5" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,17 +1090,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355446</v>
+        <v>121355471</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571453</v>
+        <v>571429</v>
       </c>
       <c r="R2" t="n">
-        <v>6450543</v>
+        <v>6450550</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355471</v>
+        <v>121355446</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +799,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571429</v>
+        <v>571453</v>
       </c>
       <c r="R3" t="n">
-        <v>6450550</v>
+        <v>6450543</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,7 +1011,7 @@
         <v>121355675</v>
       </c>
       <c r="B5" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121355471</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121355446</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>94716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +909,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R4" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,17 +975,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355675</v>
+        <v>121355740</v>
       </c>
       <c r="B5" t="n">
-        <v>94713</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1016,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571398</v>
+        <v>571385</v>
       </c>
       <c r="R5" t="n">
-        <v>6450585</v>
+        <v>6450505</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,13 +1086,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355675</v>
+        <v>121355740</v>
       </c>
       <c r="B4" t="n">
-        <v>94716</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571398</v>
+        <v>571385</v>
       </c>
       <c r="R4" t="n">
-        <v>6450585</v>
+        <v>6450505</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,13 +979,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>94716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,42 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R5" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,17 +1090,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355446</v>
+        <v>121355740</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571453</v>
+        <v>571385</v>
       </c>
       <c r="R3" t="n">
-        <v>6450543</v>
+        <v>6450505</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,13 +873,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355740</v>
+        <v>121355446</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,46 +914,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571385</v>
+        <v>571453</v>
       </c>
       <c r="R4" t="n">
-        <v>6450505</v>
+        <v>6450543</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,17 +983,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355471</v>
+        <v>121355446</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>79226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571429</v>
+        <v>571453</v>
       </c>
       <c r="R2" t="n">
-        <v>6450550</v>
+        <v>6450543</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355740</v>
+        <v>121355471</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571385</v>
+        <v>571429</v>
       </c>
       <c r="R3" t="n">
-        <v>6450505</v>
+        <v>6450550</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En tjäderhona med fyra kycklingar</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355446</v>
+        <v>121355740</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>56567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,41 +905,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571453</v>
+        <v>571385</v>
       </c>
       <c r="R4" t="n">
-        <v>6450543</v>
+        <v>6450505</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,13 +979,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>121355675</v>
       </c>
       <c r="B5" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355446</v>
+        <v>121355471</v>
       </c>
       <c r="B2" t="n">
-        <v>79226</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571453</v>
+        <v>571429</v>
       </c>
       <c r="R2" t="n">
-        <v>6450543</v>
+        <v>6450550</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355471</v>
+        <v>121355740</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>56568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571429</v>
+        <v>571385</v>
       </c>
       <c r="R3" t="n">
-        <v>6450550</v>
+        <v>6450505</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>En tjäderhona med fyra kycklingar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B4" t="n">
-        <v>56567</v>
+        <v>94723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +918,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R4" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,17 +984,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355675</v>
+        <v>121355446</v>
       </c>
       <c r="B5" t="n">
-        <v>94722</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,31 +1021,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571398</v>
+        <v>571453</v>
       </c>
       <c r="R5" t="n">
-        <v>6450585</v>
+        <v>6450543</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355471</v>
+        <v>121355675</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>94723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571429</v>
+        <v>571398</v>
       </c>
       <c r="R2" t="n">
-        <v>6450550</v>
+        <v>6450585</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355740</v>
+        <v>121355471</v>
       </c>
       <c r="B3" t="n">
-        <v>56568</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571385</v>
+        <v>571429</v>
       </c>
       <c r="R3" t="n">
-        <v>6450505</v>
+        <v>6450550</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En tjäderhona med fyra kycklingar</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355675</v>
+        <v>121355740</v>
       </c>
       <c r="B4" t="n">
-        <v>94723</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,38 +910,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571398</v>
+        <v>571385</v>
       </c>
       <c r="R4" t="n">
-        <v>6450585</v>
+        <v>6450505</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,13 +980,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355675</v>
+        <v>121355446</v>
       </c>
       <c r="B2" t="n">
-        <v>94723</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571398</v>
+        <v>571453</v>
       </c>
       <c r="R2" t="n">
-        <v>6450585</v>
+        <v>6450543</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -894,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B4" t="n">
-        <v>56568</v>
+        <v>94723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,42 +909,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R4" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,17 +975,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355446</v>
+        <v>121355740</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,41 +1012,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571453</v>
+        <v>571385</v>
       </c>
       <c r="R5" t="n">
-        <v>6450543</v>
+        <v>6450505</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,13 +1086,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355446</v>
+        <v>121355740</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>56568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571453</v>
+        <v>571385</v>
       </c>
       <c r="R2" t="n">
-        <v>6450543</v>
+        <v>6450505</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,13 +761,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En tjäderhona med fyra kycklingar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355471</v>
+        <v>121355675</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>94723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571429</v>
+        <v>571398</v>
       </c>
       <c r="R3" t="n">
-        <v>6450550</v>
+        <v>6450585</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355675</v>
+        <v>121355446</v>
       </c>
       <c r="B4" t="n">
-        <v>94723</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,31 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571398</v>
+        <v>571453</v>
       </c>
       <c r="R4" t="n">
-        <v>6450585</v>
+        <v>6450543</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355740</v>
+        <v>121355471</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,46 +1015,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571385</v>
+        <v>571429</v>
       </c>
       <c r="R5" t="n">
-        <v>6450505</v>
+        <v>6450550</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En tjäderhona med fyra kycklingar</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58164-2023 artfynd.xlsx
+++ b/artfynd/A 58164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355740</v>
+        <v>121355675</v>
       </c>
       <c r="B2" t="n">
-        <v>56568</v>
+        <v>94731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl , Sm</t>
+          <t>Öjsjön-Gåsgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571385</v>
+        <v>571398</v>
       </c>
       <c r="R2" t="n">
-        <v>6450505</v>
+        <v>6450585</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,17 +757,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En tjäderhona med fyra kycklingar</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355675</v>
+        <v>121355446</v>
       </c>
       <c r="B3" t="n">
-        <v>94723</v>
+        <v>79234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571398</v>
+        <v>571453</v>
       </c>
       <c r="R3" t="n">
-        <v>6450585</v>
+        <v>6450543</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355446</v>
+        <v>121355471</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +900,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571453</v>
+        <v>571429</v>
       </c>
       <c r="R4" t="n">
-        <v>6450543</v>
+        <v>6450550</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355471</v>
+        <v>121355740</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,42 +1012,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Gåsgöl, Sm</t>
+          <t>Öjsjön-Gåsgöl , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571429</v>
+        <v>571385</v>
       </c>
       <c r="R5" t="n">
-        <v>6450550</v>
+        <v>6450505</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>En tjäderhona med fyra kycklingar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
